--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44786</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45384</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>44574</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45392</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45446</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>46149</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45965</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45240</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45468</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45218</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44552</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45256</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45012</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>46126</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43963</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45568</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45412</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44837</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>46126</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45581</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44820</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45034</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45754</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45098</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45908</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45330</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>46139</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46097</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45468</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45540</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45175</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44620</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44866</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44851</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44477</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44539</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44546</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44483</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44497</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44866</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44544</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44768</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44704</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44488</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44477</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44712</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44711</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44865</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44596</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44712</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>44593</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44685</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44756</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44756</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44789</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44818</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44656</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44756</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44978</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44965</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45580</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45580</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45448</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45448</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45567</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45408</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44973</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45364</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45051</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45110</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45110</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45432</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>44749</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44995</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45489</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45490</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44818</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45349</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45022</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45691</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44951</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45253</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45198</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45372</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45754</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>44963</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45019</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45294</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45147</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45204</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45207</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45610</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45385</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45314</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44994</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45408</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45411</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44664</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45147</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44663</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45223</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45330</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45043</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45323</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45110</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45359</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45212</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45168</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45254</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44602</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45208</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45204</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>44711</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45021</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45369</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45369</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44817</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44818</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45240</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45212</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44862</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45096</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45034</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44914</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44914</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45113</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45337</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45274</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44836</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45007</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45254</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44467</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44963</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45908</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45216</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45834</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44963</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44970</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45763</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45379</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45784</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45530</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45252</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45968</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44984</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>44564</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45589</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45931</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45784</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45280</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45985</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45805</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45902</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45811</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45523</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45884</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45908</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45908</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45908</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44488</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45113</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45986</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45209</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45022</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45348</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>46141</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>46141</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44980</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44994</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45209</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44977</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45929</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>46141</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45929</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45929</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45929</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45931</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45931</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45931</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45931</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45930</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45930</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45930</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45930</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45930</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45931</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45075</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45931</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45469</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44613</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44539</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45258</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>46146</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45939</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>46147</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44951</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46147</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45944</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45280</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45280</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45950</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>46153</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>44978</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45957</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45961</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45580</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45041</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44987</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>44621</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>45320</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44917</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45433</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>45448</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45372</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44547</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44945</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45204</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44865</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45435</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45975</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45523</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45603</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>44621</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45373</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45098</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45208</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>44981</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45695</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>44980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45610</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44995</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45989</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44630</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44973</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45323</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45989</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45002</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45092</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45097</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45691</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45012</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45369</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44995</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44820</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45198</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45999</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46000</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46001</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46001</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46001</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45999</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46001</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45531</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44749</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45999</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45999</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44621</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45448</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45110</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45369</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45075</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45483</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45695</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45695</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45182</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>46009</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44551</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>46009</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>46009</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45110</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>44505</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45567</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44547</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45406</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45407</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45056</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>46169</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45644</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45090</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45215</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>44755</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45601</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45113</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45240</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45687</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46171</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>46171</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44494</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44879</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45526</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44951</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>46042</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44908</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>46045</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45700</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>46049</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>46175</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44713</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>46050</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45691</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>46009</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45091</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45701</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>46177</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44900</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>46058</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46058</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>46058</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46059</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45341</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>44539</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46069</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46069</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>44711</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44608</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46181</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>44624</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46182</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45256</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45195</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44620</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>44461</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45204</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45560</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>46091</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46098</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46099</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>46195</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>46196</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45240</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45691</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>46195</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>44483</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45169</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44585</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46106</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>46105</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45386</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46105</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45372</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>46197</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45317</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>46199</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46199</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46114</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>46114</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46195</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46199</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>44865</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45056</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46243</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46121</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>46126</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45448</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45448</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>46244</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45015</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>46127</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45329</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>46128</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46128</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46243</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46199</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45240</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45240</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>46203</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>45252</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>46202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45244</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45098</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46202</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45604</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45580</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45377</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45625</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>44733</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45979</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>46203</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>46007</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>45385</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>45931</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45908</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45218</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45832</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45092</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45034</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45490</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45908</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>46202</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>46198</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>46198</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45603</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44490</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46202</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>46202</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45113</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45720</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45519</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45372</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45012</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45531</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45098</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45267</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45391</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45490</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>44980</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45105</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45096</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>45041</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45985</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44943</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45405</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45405</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45531</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>44865</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>46252</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>45258</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45539</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45490</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45245</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45196</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45604</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45218</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45314</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45036</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>46211</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45553</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45110</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>46210</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>45621</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>45643</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>45708</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>44489</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>46265</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>44995</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45103</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45103</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45099</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46265</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45572</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>46266</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>44488</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46266</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45709</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45113</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>46267</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>46266</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45028</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45740</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45119</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45469</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45469</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46272</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>46230</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>46147</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45728</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45525</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45233</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45224</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45474</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45572</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45708</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45632</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45754</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45796</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45204</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>45526</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45408</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45805</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45811</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45818</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45825</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45805</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45832</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45832</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45832</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45792</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45691</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45792</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45838</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45645</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45756</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45357</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45615</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45078</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45357</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>44685</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45477</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45477</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>44594</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45195</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>44988</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45476</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45357</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45357</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45470</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>44979</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44665</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44634</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45889</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45954</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46009</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45468</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46197</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45384</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45691</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45965</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>46149</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45446</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45240</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45392</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45468</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>45701</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45701</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>46126</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45256</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44552</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45012</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43963</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45412</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45568</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>46126</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44568</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>44820</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>46097</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>45098</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>46139</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45034</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45330</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45468</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45540</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45175</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44620</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44866</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44851</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44477</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44539</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44546</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44483</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44866</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44497</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44544</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44768</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44704</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44488</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44477</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44712</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44711</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44865</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44596</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44712</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>44593</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44685</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44756</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44756</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44791</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44789</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44818</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44817</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45691</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45377</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45105</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45212</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45406</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45407</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45097</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45216</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44963</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45359</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45110</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45314</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44963</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45323</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>45490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44865</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45796</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45204</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45483</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45012</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45530</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44602</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45489</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44981</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45784</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44984</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45531</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46042</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45526</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>46045</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45811</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45408</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45523</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45784</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45280</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44994</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44914</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>46049</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>46050</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45902</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44490</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45908</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45908</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45908</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45908</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44914</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>46009</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44995</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>44539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>46058</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46058</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>46058</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>46059</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45490</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45218</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45691</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45490</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>46069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45572</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45432</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>44951</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45930</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45930</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45929</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45929</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45929</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45567</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45930</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45560</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45930</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45929</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45929</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45929</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45805</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45931</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45709</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45931</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45931</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45931</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45252</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44630</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44980</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>46091</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44467</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45372</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45253</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45448</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45944</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>46098</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>46099</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45182</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45580</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>45386</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>46105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>46105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45695</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45695</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44713</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>46106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45553</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45601</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45604</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45113</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45957</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>46114</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>46114</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>46121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45961</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45603</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>46126</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45090</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>46127</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45811</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>44987</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>46128</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44970</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45978</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45975</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>46128</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45103</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45103</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45385</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45985</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44613</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>46007</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45329</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45034</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45818</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45979</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45989</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45989</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>46007</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45408</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>44980</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45999</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45999</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>46000</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45908</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45999</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45999</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45999</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>46001</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45625</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>46001</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>46001</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>45379</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44978</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44663</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45968</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45884</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>46009</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>46009</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46009</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44818</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45267</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45832</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45348</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45041</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45012</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45092</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45110</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44733</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45110</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45245</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45198</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45825</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>46141</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>46141</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46141</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45022</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45986</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45320</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45832</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>46146</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45056</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45805</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46147</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46147</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45832</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45832</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45691</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45792</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45792</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44900</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45691</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45252</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44836</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45435</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44915</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45098</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45838</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45369</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45369</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45208</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44489</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45280</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45645</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45391</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45240</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45147</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46169</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>46171</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>46171</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45519</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45096</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46175</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44539</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44995</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44995</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44547</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>46177</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45373</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44965</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46181</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45643</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45168</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45411</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>46182</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44621</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45043</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45022</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45601</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45580</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44494</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>44573</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45580</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45223</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>46195</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45075</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45075</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46195</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45204</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>46196</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>44551</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46197</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>46199</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>46199</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>46199</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>46199</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45756</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>46203</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>46202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>46202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45644</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>46202</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>46198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>46198</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45198</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45610</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>46202</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>46202</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46203</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45834</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45567</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46252</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45091</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44547</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45208</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45385</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45691</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45985</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45708</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46211</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45204</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45207</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46210</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45531</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45687</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44711</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45098</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>44818</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44749</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45110</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45169</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45408</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45204</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44756</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45240</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46266</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46265</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>45754</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>46266</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45317</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45448</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45254</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45531</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45349</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44503</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>44917</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45330</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>44945</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46272</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45448</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45015</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45372</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45294</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46230</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45274</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>44488</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45589</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>44879</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>44621</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45215</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45523</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45539</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45448</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>45258</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>46243</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>46243</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45433</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>44488</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>44865</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>45720</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44743</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>44585</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46287</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>46288</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46288</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>46288</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>46195</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>44917</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>44951</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>46244</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45526</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45369</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46287</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45469</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44862</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>45028</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45196</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>44917</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>46199</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45405</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45405</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45256</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45034</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45209</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45056</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>44995</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>46147</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44624</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45337</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45448</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45448</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44505</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44865</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44994</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44973</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45096</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45204</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>44621</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45372</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45604</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>44963</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45098</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45163</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44564</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45021</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45007</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44483</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44980</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>44620</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>44978</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45531</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45212</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44951</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45621</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45240</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45372</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45323</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45629</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45610</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45019</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45341</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45099</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45113</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45364</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>44977</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>44987</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45113</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45218</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45051</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44755</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45041</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45240</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45168</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44749</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45195</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45700</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>44664</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45369</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45580</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45314</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44711</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45110</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45110</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44943</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45113</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45701</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45209</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45036</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45695</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45119</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45469</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45740</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45469</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45233</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45708</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45572</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45632</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45728</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45224</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45525</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45754</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45474</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>44685</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>44594</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>44665</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>44634</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45357</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45615</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45078</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45287</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45477</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45477</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>44988</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45476</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45357</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45357</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45470</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44979</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45889</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>45954</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>46009</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45468</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>46197</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45384</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45691</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45965</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>46149</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45446</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45240</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45392</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45468</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>45701</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45701</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>46126</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45256</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44552</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45012</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43963</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45412</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45568</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>46126</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44568</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>44820</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>46097</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>45098</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>46139</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44818</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45034</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45330</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45468</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45540</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45175</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44620</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44866</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44851</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44477</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44539</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44546</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44483</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44866</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44497</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44544</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44768</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44704</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44488</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44477</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44712</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44711</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44865</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44596</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44712</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>44593</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44685</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44756</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44756</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44791</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44789</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44818</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44817</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45691</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45377</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45105</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45212</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45406</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45407</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45097</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45216</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44963</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45359</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45110</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45314</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44963</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45323</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>45490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44865</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45796</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45204</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45483</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45012</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45530</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44602</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45489</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44981</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45784</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44984</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45531</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46042</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45526</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>46045</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45811</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45408</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45523</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45784</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45280</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44994</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44914</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>46049</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>46050</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45902</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44490</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45908</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45908</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45908</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45908</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44914</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>46009</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44995</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>44539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>46058</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46058</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>46058</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>46059</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45490</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45218</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45691</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45490</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>46069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45572</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45432</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>44951</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45930</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45930</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45929</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45929</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45929</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45567</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45930</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45560</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45930</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45929</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45929</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45929</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45805</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45931</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45709</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45931</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45931</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45931</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45252</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44630</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44980</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>46091</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44467</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45372</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45253</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45448</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45944</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>46098</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>46099</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45182</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45580</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>45386</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>46105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>46105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45695</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45695</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44713</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>46106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45553</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45601</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45604</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45113</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45957</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>46114</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>46114</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>46121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45961</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45603</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>46126</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45090</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>46127</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45811</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>44987</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>46128</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44970</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45978</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45975</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>46128</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45103</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45103</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45385</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45985</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44613</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>46007</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45329</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45034</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45818</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45979</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45989</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45989</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>46007</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45408</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>44980</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45999</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45999</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>46000</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45908</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45999</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45999</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45999</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>46001</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45625</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>46001</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>46001</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>45379</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44978</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44663</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45968</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45884</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>46009</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>46009</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46009</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44818</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45267</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45832</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45348</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45041</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45012</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45092</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45110</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44733</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45110</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45245</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45198</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45825</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>46141</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>46141</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46141</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45022</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45986</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45320</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45832</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>46146</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45056</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45805</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46147</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46147</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45832</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45832</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45691</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45792</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45792</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44900</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45691</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45252</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44836</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45435</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44915</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45098</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45838</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45369</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45369</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45208</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44489</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45280</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45645</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45391</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45240</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45147</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46169</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>46171</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>46171</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45519</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45096</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46175</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44539</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44995</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44995</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44547</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>46177</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45373</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44965</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46181</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45643</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45168</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45411</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>46182</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44621</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45043</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45022</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45601</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45580</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44494</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>44573</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45580</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45223</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>46195</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45075</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45075</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46195</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45204</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>46196</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>44551</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46197</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>46199</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>46199</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>46199</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>46199</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45756</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>46203</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>46202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>46202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45644</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>46202</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>46198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>46198</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45198</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45610</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>46202</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>46202</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46203</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45834</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45567</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46252</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45091</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44547</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45208</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45385</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45691</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45985</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45708</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46211</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45204</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45207</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46210</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45531</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45687</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44711</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45098</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>44818</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44749</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45110</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45169</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45408</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45204</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44756</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45240</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46266</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46265</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>45754</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>46266</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45317</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45448</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45254</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45531</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45349</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44503</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>44917</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45330</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>44945</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46272</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45448</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45015</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45372</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45294</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46230</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45274</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>44488</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45589</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>44879</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>44621</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45215</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45523</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45539</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45448</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>45258</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>46243</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>46243</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45433</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>44488</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>44865</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>45720</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44743</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>44585</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46287</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>46288</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46288</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>46288</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>46195</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>44917</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>44951</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>46244</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45526</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45369</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46287</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45469</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44862</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>45028</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45196</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>44917</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>46199</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45405</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45405</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45256</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45034</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45209</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45056</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>44995</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>46147</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44624</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45337</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45448</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45448</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44505</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44865</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44994</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44973</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45096</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45204</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>44621</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45372</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45604</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>44963</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45098</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45163</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44564</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45021</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45007</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44483</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44980</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>44620</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>44978</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45531</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45212</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44951</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45621</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45240</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45372</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45323</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45629</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45610</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45019</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45341</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45099</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45113</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45364</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>44977</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>44987</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45113</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45218</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45051</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44755</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45041</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45240</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45168</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44749</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45195</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45700</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>44664</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45369</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45580</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45314</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44711</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45110</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45110</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44943</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45113</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45701</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45209</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45036</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45695</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45119</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45469</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45740</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45469</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45233</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45708</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45572</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45632</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45728</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45224</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45525</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45754</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45474</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>44685</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>44594</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>44665</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>44634</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45357</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45615</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45078</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45287</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45477</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45477</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>44988</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45476</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45357</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45357</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45470</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44979</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45889</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>45954</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>46009</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45468</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>46197</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44786</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>44574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45384</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45691</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45392</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45965</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45446</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>46149</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45240</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45468</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45218</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44552</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45256</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>46126</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45012</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43963</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45568</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>46126</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45412</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>44837</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45113</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45175</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>44820</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46097</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>45098</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45799</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45330</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>46139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45700</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44818</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>45468</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45540</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44620</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44866</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44851</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44477</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44539</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44546</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44483</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44866</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44497</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44573</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44544</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44768</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44704</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44477</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44712</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44869</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44711</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44865</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>44596</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44712</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44685</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44756</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44756</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44818</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44656</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44978</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45531</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45580</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45580</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45448</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45448</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45567</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44973</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45408</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45364</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45110</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45110</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44743</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45474</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45572</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45708</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45999</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45632</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45754</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>44573</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45432</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45629</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45372</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46009</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>46009</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>46009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>44995</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44818</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45489</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45490</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45349</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45691</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45022</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45253</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45784</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44963</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45019</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45902</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45523</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45482</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45908</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45754</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45908</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45908</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45908</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45796</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45294</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>46045</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45204</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45204</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45163</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>46049</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45526</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45408</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45408</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45212</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45147</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45805</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46009</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45207</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45314</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45610</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45385</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45929</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>46058</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45929</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45929</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45929</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>46058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>46058</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45929</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45931</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>46059</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45931</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45931</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45929</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45930</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45930</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45811</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45931</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45931</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45411</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45147</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44663</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>46069</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>46069</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45939</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45223</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45323</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45944</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45330</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45043</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45110</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45359</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45254</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44602</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45208</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45369</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45369</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45961</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45021</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>44817</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45212</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44711</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>44818</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45240</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44862</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>46098</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45096</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45975</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45337</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>44914</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44914</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45818</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>46106</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45386</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45601</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45113</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>46105</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45274</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45007</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>46114</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>44836</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45825</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45989</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>44963</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>46121</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45216</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>46126</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46127</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44963</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>44970</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>46128</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45999</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45999</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>46000</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46001</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>46001</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45805</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45999</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45832</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45832</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45832</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45530</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45252</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45691</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44984</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45792</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44564</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45979</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45838</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>46007</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45931</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45908</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45589</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45832</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45908</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45280</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45908</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45645</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45763</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>44488</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45209</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45379</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44980</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45968</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44994</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45209</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45931</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44977</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45985</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46007</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45884</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45075</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45469</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>44613</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45986</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>44539</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45258</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45022</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45348</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44951</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>46141</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46141</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45280</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45280</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>46141</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44978</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46147</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46147</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>46153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45580</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45041</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44987</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>44621</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45320</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>44917</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45433</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45448</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45372</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44547</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44945</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>45204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44987</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45691</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>44865</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45435</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45523</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45603</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44621</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45373</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45098</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45208</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>44981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45695</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44980</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>46169</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45610</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>44995</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>46171</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>46171</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44630</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>44973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45323</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45097</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45756</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45012</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45834</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>46177</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45369</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44995</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>44820</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46181</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45099</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44917</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>46182</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44915</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45531</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>44749</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44621</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45448</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45110</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45369</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45075</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45483</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45695</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45695</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45182</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>44551</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>46195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46196</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45110</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>44505</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45567</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44547</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>46199</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45406</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45407</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45056</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45644</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46197</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45215</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46199</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>46199</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>44755</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45601</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46199</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46203</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>46202</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46202</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45687</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46203</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>46202</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>46198</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46198</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46202</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>44494</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44879</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45985</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45526</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>44951</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46211</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44908</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45700</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44713</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45691</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45091</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45701</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>44900</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45341</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>46266</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44539</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>46266</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44711</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>46267</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>44608</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>46266</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>44624</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>45256</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45195</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44620</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46272</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45560</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45240</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45691</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44483</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45169</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44585</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46287</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45372</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46244</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>46287</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46243</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45317</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46243</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46288</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>44865</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>46288</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46195</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45056</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45448</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45448</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46147</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45015</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45329</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45240</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45240</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45252</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45244</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46199</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45604</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46128</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45580</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45377</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45625</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>44733</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45385</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45218</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45092</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45034</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46252</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45490</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45603</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44490</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44711</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>46295</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45113</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45720</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45519</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45372</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45012</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45531</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46210</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46296</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45267</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45391</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45490</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44980</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45105</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45096</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45041</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>44943</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45405</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45405</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45531</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>44865</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45258</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45539</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45490</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45245</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45196</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45604</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45218</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45168</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45314</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45036</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45553</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45110</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45621</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45643</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45708</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44489</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44995</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45103</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45103</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45099</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45572</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>44488</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45113</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45028</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45740</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45119</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45469</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45469</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45728</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45525</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45233</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45224</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45357</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45615</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45078</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45357</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>44685</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45477</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45477</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>44594</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45195</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>44988</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45476</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45357</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45357</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45470</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>44979</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44665</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44634</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45889</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45954</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46009</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45468</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46197</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44786</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>44574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45384</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45691</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45392</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45965</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45446</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>46149</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45240</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45468</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45218</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44552</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45256</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>46126</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45012</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43963</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45568</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>46126</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45412</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>44837</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45113</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45175</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>44820</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46097</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>45098</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45799</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45330</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>46139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46184</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45700</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44818</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>45468</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45540</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44620</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44866</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44851</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44477</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44539</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44546</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44483</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44866</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44497</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44573</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44544</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44768</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44704</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44477</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44712</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44869</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44711</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44865</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>44596</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44712</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44685</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44756</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44756</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44818</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44656</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44978</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45531</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45580</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45580</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45448</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45448</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45567</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44973</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45408</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45364</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45110</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45110</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44743</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45474</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45572</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45708</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45999</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45632</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45754</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>44573</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45432</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45629</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45372</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46009</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>46009</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>46009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>44995</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44818</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45489</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45490</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45349</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45691</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45022</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45253</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45784</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44963</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45019</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45902</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45523</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45482</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45908</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45754</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45908</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45908</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45908</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45796</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45294</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>46045</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45204</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45204</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45163</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>46049</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45526</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45408</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45408</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45212</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45147</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45805</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46009</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45207</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45314</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45610</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45385</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45929</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>46058</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45929</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45929</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45929</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>46058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>46058</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45929</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45931</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>46059</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45931</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45931</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45929</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45930</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45930</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45811</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45931</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45931</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45411</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45147</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44663</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>46069</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>46069</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45939</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45223</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45323</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45944</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45330</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45043</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45110</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45359</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45254</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44602</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45208</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45369</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45369</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45961</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45021</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>44817</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45212</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44711</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>44818</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45240</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44862</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>46098</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45096</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45975</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45337</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>44914</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44914</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45818</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>46106</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45386</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45601</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45113</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>46105</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45274</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45007</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>46114</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>44836</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45825</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45989</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>44963</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>46121</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45216</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>46126</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46127</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44963</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>44970</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>46128</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45999</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45999</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>46000</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46001</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>46001</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45805</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45999</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45832</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45832</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45832</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45530</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45252</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45691</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44984</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45792</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44564</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45979</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45838</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>46007</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45931</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45908</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45589</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45832</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45908</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45280</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45908</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45645</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45763</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>44488</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45209</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45379</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44980</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45968</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44994</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45209</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45931</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44977</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45985</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46007</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45884</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45075</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45469</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>44613</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45986</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>44539</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45258</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45022</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45348</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44951</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>46141</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46141</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45280</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45280</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>46141</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44978</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46147</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46147</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>46153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45580</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45041</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44987</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>44621</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45320</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>44917</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45433</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45448</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45372</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44547</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44945</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>45204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44987</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45691</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>44865</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45435</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45523</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45603</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44621</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45373</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45098</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45208</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>44981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45695</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44980</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>46169</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45610</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>44995</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>46171</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>46171</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44630</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>44973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45323</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45097</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45756</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45012</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45834</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>46177</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45369</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44995</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>44820</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46181</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45099</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44917</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>46182</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44915</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45531</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>44749</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44621</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45448</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45110</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45369</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45075</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45483</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45695</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45695</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45182</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>44551</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>46195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46196</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45110</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>44505</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45567</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44547</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>46199</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45406</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45407</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45056</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45644</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46197</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45215</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46199</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>46199</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>44755</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45601</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46199</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46203</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>46202</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46202</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45687</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46203</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>46202</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>46198</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46198</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46202</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>44494</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44879</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45985</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45526</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>44951</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46211</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44908</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45700</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44713</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45691</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45091</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45701</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>44900</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45341</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>46266</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44539</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>46266</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44711</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>46267</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>44608</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>46266</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>44624</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>45256</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45195</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44620</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46272</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45560</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45240</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45691</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44483</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45169</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44585</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46287</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45372</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46244</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>46287</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46243</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45317</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46243</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46288</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>44865</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>46288</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46195</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45056</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45448</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45448</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46147</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45015</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45329</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45240</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45240</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45252</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45244</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46199</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45604</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46128</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45580</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45377</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45625</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>44733</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45385</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45218</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45092</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45034</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46252</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45490</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45603</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>44490</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44711</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>46295</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45113</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45720</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45519</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45372</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45012</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45531</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46210</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46296</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45267</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45391</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45490</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44980</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45105</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45096</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45041</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>44943</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45405</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45405</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45531</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>44865</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45258</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45539</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45490</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45245</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45196</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45604</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45218</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45168</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45314</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45036</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45553</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45110</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45621</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45643</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45708</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44489</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44995</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45103</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45103</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45099</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45572</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>44488</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45113</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45028</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45740</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45119</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45469</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45469</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45728</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45525</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45233</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45224</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45357</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45615</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45078</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45357</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>44685</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45477</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45477</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>44594</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45195</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>44988</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45476</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45357</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45357</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45470</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>44979</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44665</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44634</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45889</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45954</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46009</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45468</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46197</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46149</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>46063</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45384</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45691</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45240</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45392</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46149</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45468</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>46183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45218</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45175</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45701</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44552</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45012</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45256</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>46126</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43963</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45412</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45568</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46126</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44494</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44820</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45330</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45468</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45540</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45175</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>45581</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>45700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>46097</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44818</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45034</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>46139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>46301</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44620</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>44866</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44851</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>44761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>44865</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44596</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44546</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44621</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44483</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44768</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>44596</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44712</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>44713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44712</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44497</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44704</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44869</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44488</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44711</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44685</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>44756</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44756</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45406</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45407</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44789</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>44820</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44818</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45610</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45097</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45019</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45341</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45113</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>45364</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45216</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45377</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44977</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44987</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>44900</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45252</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44836</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45435</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45218</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45051</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45092</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45369</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45369</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44755</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45208</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45041</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45002</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45240</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45105</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44489</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45280</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45280</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45391</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44963</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45258</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45195</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45240</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45240</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45700</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45359</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44664</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45834</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45369</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45110</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45580</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45314</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44711</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45314</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44963</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45323</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45490</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44865</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45784</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45483</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45110</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45110</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45519</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45096</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45490</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45482</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45012</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45530</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>44943</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>44602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45489</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45811</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44981</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44984</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45523</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45701</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45784</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45805</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45695</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44995</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44995</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44656</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45902</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44547</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45908</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45908</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45908</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45373</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45908</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45119</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45469</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45740</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45469</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>44994</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44914</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44490</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45643</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45168</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45411</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45233</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44914</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44621</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45708</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44995</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45043</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45022</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45601</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45632</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45490</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45728</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45691</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45224</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45580</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45525</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45490</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>44494</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45754</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44573</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45474</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45580</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45223</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45075</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45075</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45572</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45432</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45930</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44951</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45929</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44551</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45929</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45929</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45930</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45930</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45567</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45930</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45929</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45929</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45929</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45929</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45560</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45796</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45931</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45204</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45252</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44630</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45931</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44980</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45644</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45931</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45372</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45198</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45610</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45253</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45526</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45408</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45448</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45567</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45182</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45805</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>44547</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45208</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45580</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45385</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45691</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45695</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45695</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44713</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>44608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45939</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45708</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45553</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45603</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45204</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45944</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45601</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45207</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45811</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45604</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45818</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45531</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45147</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45099</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45687</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45254</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45603</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44711</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45825</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45244</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45832</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44987</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45805</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45832</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44818</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45957</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45691</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45113</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45792</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45792</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44970</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45103</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45103</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45838</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>44749</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45385</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45110</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45169</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44613</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45329</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45408</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45204</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45034</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45645</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>44756</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45240</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>44973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45754</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45317</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45975</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45408</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>44980</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45448</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45254</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45531</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45625</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45349</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>44503</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44917</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45330</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44945</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45448</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>44663</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45015</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45372</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44818</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45294</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45267</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45041</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45012</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45274</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44488</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45110</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45756</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44733</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45110</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46098</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45589</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>46099</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45245</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44879</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44621</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45386</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46105</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45215</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>46105</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>46106</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45320</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45523</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45539</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>45448</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45989</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45989</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45258</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45056</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46114</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45433</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44488</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44865</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>46121</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45720</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44743</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44585</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46126</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45999</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45999</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>46000</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45999</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45999</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45999</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>46001</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46001</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46128</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44917</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>44951</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>46001</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46001</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45526</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45369</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45763</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>44862</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45985</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46007</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45028</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45196</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44917</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45908</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45979</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45405</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45405</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45256</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>46009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>46009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>46009</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>46007</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45034</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45209</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45056</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44995</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44624</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45337</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45448</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45448</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>44505</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45931</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45908</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45908</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44865</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44994</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44973</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45096</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>45931</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45204</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45379</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>44621</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45372</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45604</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45968</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44963</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45098</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45163</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45884</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46042</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44564</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45021</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45007</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45832</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45348</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44483</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>44980</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>44620</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44978</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>46045</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45531</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45212</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44951</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45621</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45240</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46141</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>46141</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>46141</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>45022</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45372</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45323</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>45629</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>46049</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>46050</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45986</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46009</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>46058</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>46058</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46058</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>46059</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>46146</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46147</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46147</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46069</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46069</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45691</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>46169</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>46171</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>46171</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46175</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>46177</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46182</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46195</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>46195</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46196</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>46197</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46199</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>46199</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>46199</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>46203</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>46202</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>46202</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>46202</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>46198</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>46198</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41645,7 +41645,7 @@
         <v>46202</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46202</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>46203</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>46211</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>46266</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46266</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>46265</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>46266</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>46267</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>46272</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>46230</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>46243</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>46243</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>46287</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>46288</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>46288</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>46288</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>46195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>46244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>46287</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>46199</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>46147</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>46128</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46252</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>46296</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>46295</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>46210</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>44711</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46302</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>44685</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>44594</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>44665</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>44634</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>45357</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45615</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45078</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45357</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45477</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45477</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45195</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>44988</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45476</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45357</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45357</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45470</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>44979</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45889</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45954</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>46009</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45468</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>46197</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46149</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>46063</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45384</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>44574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45691</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45240</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45392</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46149</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45468</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>46183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45218</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45175</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45701</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>44552</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45012</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45256</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>46126</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43963</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45412</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45568</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46126</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44494</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44820</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45330</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45468</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45540</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45175</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>45581</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>45700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>46097</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44818</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45034</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>46139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>46184</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>46301</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44620</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>44866</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44851</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>44761</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>44865</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44596</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44546</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44621</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44483</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44768</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>44596</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44712</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>44713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44712</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44497</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44704</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44869</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44488</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44711</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44685</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>44756</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44756</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45406</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45407</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44789</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>44820</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44818</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45610</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45097</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45019</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45341</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45113</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>45364</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45216</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45377</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44977</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44987</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>44900</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45252</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44836</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45435</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45218</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45051</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45092</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45369</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45369</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44755</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45208</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45041</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45002</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45240</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45105</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44489</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45280</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45280</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45391</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44963</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45258</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45195</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45240</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45240</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45700</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45359</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44664</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45834</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45369</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45110</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45580</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45314</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44711</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45314</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44963</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45323</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45490</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44865</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45784</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45483</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45110</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45110</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45519</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45096</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45490</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45482</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45012</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45530</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>44943</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>44602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45489</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45811</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44981</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44984</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45523</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45701</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45784</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45805</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45695</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44995</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44995</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44656</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45902</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44547</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45908</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45908</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45908</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45373</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45908</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45119</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45469</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45740</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45469</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>44994</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44914</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44490</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45643</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45168</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45411</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45233</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44914</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44621</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45708</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44995</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45043</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45022</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45601</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45632</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45490</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45728</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45691</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45224</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45580</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45525</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45490</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>44494</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45754</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44573</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45474</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45580</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45223</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45075</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45075</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45572</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45432</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45930</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44951</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45929</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44551</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45929</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45929</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45930</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45930</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45567</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45930</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45929</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45929</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45929</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45929</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45560</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45796</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45931</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45204</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45252</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44630</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45931</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44980</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45644</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45931</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45372</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45198</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45610</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45253</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45526</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45408</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45448</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45567</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45182</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45805</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>44547</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45208</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45580</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45385</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45691</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45695</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45695</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44713</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>44608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45939</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45708</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45553</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45603</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45204</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45944</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45601</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45207</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45811</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45604</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45818</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45531</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45147</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45099</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45687</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45254</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45603</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44711</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45825</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45244</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45832</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44987</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45805</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45832</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44818</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45957</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45691</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45113</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45792</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45792</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44970</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45103</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45103</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45838</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>44749</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45385</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45110</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45169</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44613</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45329</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45408</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45204</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45034</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45645</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>44756</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45240</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>44973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45754</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45317</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45975</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45408</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>44980</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45448</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45254</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45531</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45625</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45349</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>44503</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44917</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45330</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44945</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45448</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>44663</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45015</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45372</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44818</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45294</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45267</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45041</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45012</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45274</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44488</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45110</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45756</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44733</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45110</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46098</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45589</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>46099</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45245</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44879</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44621</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45386</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46105</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45215</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>46105</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>46106</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45320</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45523</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45539</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>45448</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45989</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45989</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45258</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45056</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46114</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45433</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44488</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44865</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>46121</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45720</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44743</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44585</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46126</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45999</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45999</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>46000</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45999</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45999</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45999</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>46001</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46001</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46128</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44917</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>44951</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>46001</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46001</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45526</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45369</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45763</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>44862</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45985</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46007</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45028</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45196</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44917</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45908</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45979</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45405</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45405</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45256</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>46009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>46009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>46009</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>46007</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45034</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45209</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45056</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44995</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44624</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45337</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45448</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45448</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>44505</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45931</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45908</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45908</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44865</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44994</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44973</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45096</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>45931</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45204</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45379</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>44621</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45372</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45604</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45968</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44963</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45098</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45163</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45884</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46042</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44564</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45021</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45007</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45832</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45348</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44483</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>44980</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>44620</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44978</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>46045</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45531</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45212</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44951</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45621</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45240</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46141</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>46141</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>46141</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>45022</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45372</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45323</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>45629</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>46049</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>46050</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45986</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46009</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>46058</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>46058</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46058</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>46059</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>46146</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46147</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46147</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46069</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46069</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45691</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>46169</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>46171</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>46171</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46175</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>46177</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46182</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46195</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>46195</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46196</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>46197</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46199</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>46199</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>46199</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>46203</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>46202</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>46202</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>46202</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>46198</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>46198</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41645,7 +41645,7 @@
         <v>46202</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46202</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>46203</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>46211</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>46266</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46266</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>46265</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>46266</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>46267</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>46272</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>46230</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>46243</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>46243</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>46287</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>46288</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>46288</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>46288</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>46195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>46244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>46287</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>46199</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>46147</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>46128</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46252</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>46296</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>46295</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>46210</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>44711</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46302</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>44685</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>44594</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>44665</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>44634</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>45357</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45615</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45078</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45357</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45477</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45477</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45195</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>44988</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45476</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45357</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45357</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45470</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>44979</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45889</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45954</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>46009</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45468</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>46197</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44786</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45384</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44574</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45392</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46149</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45240</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45468</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>45175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44552</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45256</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>45012</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>46126</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>43963</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>44593</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44568</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45412</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44837</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46126</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44494</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44515</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44820</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45098</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45908</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>46097</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45799</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44818</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>46301</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45468</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45540</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>45175</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44592</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44489</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44620</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44778</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44489</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44866</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44546</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44603</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44851</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44855</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44761</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44539</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44546</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44866</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44497</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>44573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44544</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44768</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44704</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>44488</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44621</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44596</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44869</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44711</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44865</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44712</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44685</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44756</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44756</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44791</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44627</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44756</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44978</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44965</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45531</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45580</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45580</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45448</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45448</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45567</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45408</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44743</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45364</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>45110</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45110</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45051</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45432</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>44749</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45629</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45372</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45489</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>44995</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45349</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45022</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45253</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44818</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44951</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44573</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45482</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45198</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>44963</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45019</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45754</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45294</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45204</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45408</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45207</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45610</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45385</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45314</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44663</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45223</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45330</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45043</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45323</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45411</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45110</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45359</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45208</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45168</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45254</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44602</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45204</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45021</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45369</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45369</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44817</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44711</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44818</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45212</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44862</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45096</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44914</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44914</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45601</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45337</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45147</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45908</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44836</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45834</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45763</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45254</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45379</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44963</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45968</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45216</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45784</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44963</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44970</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45985</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45530</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45884</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45252</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45784</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45986</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45022</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45348</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45805</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>44984</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>46141</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>46141</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45902</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45811</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45523</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44564</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45908</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45908</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45908</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45589</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46141</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>46146</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>46147</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>44488</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45113</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45209</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>46147</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45929</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45929</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45929</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45929</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45929</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45929</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45931</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45931</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45931</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45931</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45929</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>44980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45930</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45930</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45930</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45930</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45930</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45931</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45931</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>44994</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45209</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44977</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45075</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45469</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44613</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44539</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45258</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44951</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45961</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45280</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45691</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45975</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45580</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45041</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44987</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44621</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45320</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44917</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45433</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45448</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45372</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45989</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45989</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45204</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44987</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44865</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45435</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46169</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45523</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45999</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45999</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>46000</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46001</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>46001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45603</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44621</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45373</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45098</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46001</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45999</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45208</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>44981</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45695</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>46171</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44980</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>46171</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45610</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44995</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>46009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>44973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45323</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46009</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46009</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45002</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45092</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45097</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45012</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45369</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44995</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44820</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46175</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45099</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44917</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44915</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>46177</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45531</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44749</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44621</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>46042</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45448</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46045</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45110</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45369</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45075</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45483</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>46049</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45695</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45695</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44551</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>46050</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>46181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>46009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45110</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>44505</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46182</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45567</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>44547</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45406</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45407</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>46058</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45056</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46058</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>46058</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46059</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45644</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45090</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45215</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>46069</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>46069</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>44755</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45601</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>45113</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45240</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>45687</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44494</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44879</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45526</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>44951</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44908</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45700</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>46195</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>46196</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44713</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>46195</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45691</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45091</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46106</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46105</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45386</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>45701</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>46199</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>44900</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>46197</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>46114</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45341</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44539</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>46199</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>44711</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>46121</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46199</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46126</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44608</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44624</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46127</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45256</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46128</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45195</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46199</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46203</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44620</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>46202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>46202</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>46203</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46202</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45979</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>46198</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>46007</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>45931</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>46202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>46202</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45908</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45832</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45908</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45560</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45691</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>46211</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>44585</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45372</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45317</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44865</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45056</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45448</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45448</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>46230</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45015</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45329</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45240</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45240</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45098</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45604</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45580</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45377</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45625</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>44733</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45385</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45218</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45092</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45034</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45490</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45603</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44490</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45113</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45720</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45519</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45372</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45012</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45531</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45098</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45267</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45391</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>46287</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>45490</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44980</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45105</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45096</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45041</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>44943</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>46244</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>46287</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45405</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>45405</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45531</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46243</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>44865</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46243</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45539</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45490</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>46288</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45245</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>46288</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45196</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45604</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45218</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>45168</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45314</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45036</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45553</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45110</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>46199</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46128</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45621</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45643</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45708</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>44489</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45103</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45103</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>46252</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45099</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45572</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44488</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44711</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>46295</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>45113</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>46210</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>46296</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45028</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45740</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45119</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45469</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45469</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45728</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45525</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45233</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45224</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45474</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45572</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45708</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45632</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45754</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>46302</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45796</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>46307</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45204</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45526</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>46309</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45408</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>46309</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>46266</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>46265</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>45805</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45811</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>46266</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46266</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45818</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46147</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45825</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46267</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>45805</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45832</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45832</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45832</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45792</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45691</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45792</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45838</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45645</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45756</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45357</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>45615</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45078</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45357</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>44685</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>45287</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45477</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45477</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>44594</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45195</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44988</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45476</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45357</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>45470</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>44979</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44665</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>44634</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45889</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45954</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>46009</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45468</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>46197</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44786</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45384</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44574</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45392</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>46149</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45240</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45468</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>45175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44552</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45256</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>45012</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>46126</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>43963</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>44593</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44568</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45412</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44837</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46126</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44494</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44515</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44820</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45098</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45908</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>46097</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45799</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44818</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>46301</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45468</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45540</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>45175</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44592</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44489</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44620</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44778</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44489</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44866</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44546</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44603</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44851</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44855</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44761</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44539</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44546</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44866</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44497</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>44573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44544</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44768</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44704</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>44488</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44621</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44596</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44869</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44711</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44865</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44596</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44712</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44685</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44756</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44756</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44791</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44627</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44756</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44978</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44965</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45531</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45580</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45580</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45448</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45448</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45567</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45408</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44743</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45364</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>45110</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45110</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45051</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45432</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>44749</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45629</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45372</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45489</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>44995</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45349</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45022</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45253</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44818</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44951</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44573</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45482</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45198</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>44963</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45019</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45754</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45294</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45204</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45408</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45207</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45610</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45385</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45314</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44663</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45223</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45330</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45043</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45323</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45411</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45110</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45359</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45208</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45168</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45254</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44602</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45204</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45021</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45369</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45369</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44817</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44711</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44818</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45212</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44862</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45096</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44914</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44914</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45601</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45337</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45147</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45908</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44836</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45834</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45763</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45254</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45379</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44963</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45968</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45216</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45784</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44963</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44970</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45985</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45530</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45884</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45252</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45784</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45986</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45022</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45348</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45805</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>44984</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>46141</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>46141</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45902</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45811</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45523</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44564</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45908</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45908</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45908</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45589</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46141</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>46146</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>46147</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>44488</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45113</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45209</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>46147</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45929</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45929</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45929</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45929</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45929</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45929</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45931</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45931</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45931</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45931</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45929</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>44980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45930</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45930</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45930</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45930</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45930</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45931</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45931</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>44994</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45209</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44977</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45075</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45469</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44613</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44539</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45258</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44951</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45961</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45280</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45691</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45975</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45580</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45041</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44987</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44621</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45320</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>44917</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45433</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45448</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45372</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45989</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45989</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45204</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44987</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44865</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45435</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46169</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45523</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45999</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45999</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>46000</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46001</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>46001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45603</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44621</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45373</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45098</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46001</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45999</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45208</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>44981</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45695</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>46171</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>44980</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>46171</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45610</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44995</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>46009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>44973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45323</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46009</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46009</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45002</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45092</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45097</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45012</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45369</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44995</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44820</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46175</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45099</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44917</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44915</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>46177</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45531</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44749</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44621</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>46042</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45448</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46045</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45110</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45369</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45075</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45483</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>46049</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45695</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45695</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44551</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>46050</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>46181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>46009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45110</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>44505</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46182</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45567</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>44547</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45406</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45407</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>46058</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45056</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46058</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>46058</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46059</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45644</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45090</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45215</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>46069</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>46069</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>44755</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45601</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>45113</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45240</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>45687</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44494</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44879</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45526</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>44951</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44908</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45700</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>46195</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>46196</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44713</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>46195</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45691</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45091</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46106</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46105</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45386</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>45701</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>46199</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>44900</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>46197</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>46114</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45341</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44539</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>46199</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>44711</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>46121</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46199</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46126</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44608</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44624</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46127</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45256</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46128</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45195</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46199</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46203</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44620</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>46202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>46202</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>46203</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46202</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45979</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>46198</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>46007</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>45931</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>46202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>46202</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45908</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45832</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45908</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45560</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45691</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>46211</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>44585</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45372</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45317</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44865</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45056</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45448</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45448</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>46230</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45015</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45329</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45240</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45240</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45098</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45604</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45580</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45377</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45625</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>44733</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45385</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45218</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45092</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45034</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45490</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45603</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44490</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45113</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45720</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45519</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45372</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45012</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45531</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45098</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45267</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45391</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>46287</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>45490</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44980</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45105</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45096</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45041</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>44943</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>46244</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>46287</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45405</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>45405</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45531</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46243</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>44865</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46243</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45539</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45490</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>46288</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45245</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>46288</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45196</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45604</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45218</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>45168</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45314</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45036</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45553</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45110</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>46199</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46128</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45621</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45643</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45708</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>44489</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45103</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45103</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>46252</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45099</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45572</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44488</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44711</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>46295</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>45113</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>46210</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>46296</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45028</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45740</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45119</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45469</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45469</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45728</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45525</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45233</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45224</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45474</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45572</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45708</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45632</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45754</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>46302</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45796</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>46307</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45204</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45526</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>46309</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45408</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>46309</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>46266</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>46265</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>45805</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45811</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>46266</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46266</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45818</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46147</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45825</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46267</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>45805</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45832</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45832</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45832</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45792</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45691</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45792</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45838</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45645</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45756</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45357</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>45615</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45078</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45357</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>44685</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>45287</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45477</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45477</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>44594</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45195</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44988</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45476</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45357</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>45470</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>44979</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44665</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>44634</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45889</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45954</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>46009</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45468</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>46197</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>46063</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45384</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45446</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>45240</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>45965</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45392</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>46149</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45468</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>45218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45256</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44552</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>45012</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>43963</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>44593</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44837</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45412</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45568</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46126</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44494</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44515</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45754</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45034</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45908</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44820</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>46184</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>45468</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45540</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45175</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>46097</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>46301</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46315</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>46139</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44620</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>44778</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44613</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44866</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44515</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44603</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44580</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>44516</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>44855</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44761</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44588</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44539</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44539</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>44866</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44497</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>44573</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>44768</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44704</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44621</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>44712</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44711</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44869</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44865</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44596</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44713</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44712</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44593</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44685</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44756</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44756</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44789</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44818</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44818</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>44627</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45469</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44862</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>45784</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44817</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45377</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45691</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45028</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45196</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>45405</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>45405</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>45256</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>45105</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45811</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45209</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>45056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44995</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>45523</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45784</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45805</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44624</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45337</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45406</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45407</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45448</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45448</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>45902</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45908</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>44505</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45908</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45908</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44865</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>44820</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44973</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45096</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45204</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45372</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45604</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44963</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45098</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44564</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45021</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45007</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45930</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45930</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45929</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45930</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45930</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45929</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45929</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>46171</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45931</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44980</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44620</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>44978</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45931</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45931</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45931</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45931</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>46171</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45931</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45531</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45212</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44951</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45621</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45240</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>46175</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45323</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45629</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45939</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45216</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45944</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46177</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45019</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45341</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45002</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45113</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45364</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44977</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44987</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46181</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>46182</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45113</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45218</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45957</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45051</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>44963</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44755</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45961</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45240</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45258</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45168</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44749</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45700</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>46195</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>44664</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45369</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45580</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46196</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45314</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44711</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>46197</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>46199</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45359</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>46199</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>46199</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>46203</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>46202</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46202</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>46202</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>46198</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>46202</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>46202</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>46203</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45110</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45110</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45110</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44943</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45985</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>46211</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45113</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45701</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45989</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45209</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45314</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45036</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>44963</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45323</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45695</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45999</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>45999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45999</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45999</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45999</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>46001</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45469</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45740</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>46001</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45469</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45490</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>46001</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46230</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45233</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45708</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45572</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44865</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>46009</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46009</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>46009</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45632</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45728</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45224</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45525</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45754</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45474</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>46243</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>46243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45796</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>46042</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>46287</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>46288</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>46288</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>46288</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>46195</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>46244</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>46045</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>46287</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45526</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45408</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>46049</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46050</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>46199</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45805</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>46009</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>46058</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>46058</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46059</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>46128</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45811</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45818</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>46069</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45483</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>46069</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>46252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46296</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46295</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45832</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>45805</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45832</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45691</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45490</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45792</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45792</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46210</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45482</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44711</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45012</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45838</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45530</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46098</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46099</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44602</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45489</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45645</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45386</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>46105</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46105</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46106</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>46302</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>44981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44984</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>46114</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46121</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>46126</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46127</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44656</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>46128</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45756</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>46265</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>44908</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46307</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45834</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45280</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44994</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44914</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45763</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45985</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>46007</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45908</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>44914</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45979</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>46266</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46309</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>44995</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>46007</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46309</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>44539</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45490</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>46267</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45218</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45691</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>46266</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45931</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45908</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45908</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45490</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45931</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45379</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45968</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45572</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45432</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45884</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46314</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44951</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45832</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45348</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>46272</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45567</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45560</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45252</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44630</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>46141</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>46141</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>46141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45022</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44980</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45986</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45372</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>46146</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>45448</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>46147</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>46147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>45182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45580</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45695</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45695</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44713</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45553</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45603</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45601</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45604</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45691</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45603</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45090</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45244</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44987</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44970</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45103</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>45103</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45385</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>44613</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45329</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45034</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>44973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45408</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45625</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44978</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44663</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>44818</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45267</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45041</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45012</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45092</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45110</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>44733</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>45110</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45245</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45198</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45320</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45056</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44900</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45252</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>44836</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45435</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44915</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45098</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45092</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45369</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45369</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45208</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45280</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45280</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45391</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45240</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45240</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45147</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45519</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45096</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>44539</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44995</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>44995</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>44547</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45373</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44965</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45643</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45411</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>44621</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45043</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45022</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45601</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45580</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>44494</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44573</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45580</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45223</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45075</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45204</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44551</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45644</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45198</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45610</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45567</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45091</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>44547</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45208</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45385</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45691</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>44608</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45708</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45204</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45207</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45531</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45147</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45687</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45254</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44711</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>45098</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>44818</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45113</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>44749</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45110</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45169</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45408</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45204</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>44756</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45240</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45754</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45317</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45448</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45254</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45531</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45349</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>44503</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>44917</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45330</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>44945</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45448</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>45015</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45372</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>45294</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>45274</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45589</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>44879</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44621</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45215</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45523</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>45539</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>45448</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45258</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45433</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44865</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45720</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>44743</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>44585</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>44917</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>44951</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45526</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45369</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>44685</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44594</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>44665</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44634</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>45357</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45615</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45078</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45357</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>45287</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>45477</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45477</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45195</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>44988</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45476</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45357</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45470</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>44979</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45889</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45954</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>46009</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45468</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>46197</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44984</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46079</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45170</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44916</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45715</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>44798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>46063</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45722</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46211</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45384</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45446</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>45240</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>45965</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45392</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>46149</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45468</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>45218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45701</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45256</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44552</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>45012</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>43963</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>44593</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44837</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45412</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45568</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46126</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44494</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44515</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45754</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45034</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45908</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44820</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>46184</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>45468</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45540</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45175</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>46097</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>46301</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46315</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>46139</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44620</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>44778</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44613</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44866</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44515</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44603</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44580</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>44516</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>44855</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44761</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44588</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44539</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44539</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>44866</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44497</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>44573</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>44768</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44704</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44621</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>44712</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44711</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44869</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44865</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>44596</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44713</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44712</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44593</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44685</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44756</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44756</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44789</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44818</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44818</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>44627</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45469</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44862</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>45784</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44817</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45377</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45691</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45028</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45196</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>45405</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>45405</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>45256</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>45105</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>45034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45811</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45209</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>45056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44995</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>45523</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45784</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45805</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44624</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45337</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45406</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45407</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45448</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45448</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>45902</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45908</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>44505</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45908</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45908</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44865</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>44820</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44973</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45096</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45204</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45372</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45604</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44963</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45098</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44564</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45021</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45007</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45930</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45930</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45929</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45930</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45930</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45929</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45929</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>46171</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45931</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44980</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44620</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>44978</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45931</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45931</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45931</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45931</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>46171</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45931</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45531</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45212</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44951</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45621</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45240</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>46175</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45323</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45629</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45939</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45216</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45944</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46177</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45019</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45341</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45002</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45113</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45364</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44977</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44987</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46181</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>46182</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45113</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45218</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45957</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45051</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>44963</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44755</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45961</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45240</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45258</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45168</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44749</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45700</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>46195</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>44664</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45369</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45580</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46196</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45314</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44711</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>46197</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>46199</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45359</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>46199</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>46199</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>46203</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>46202</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46202</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>46202</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>46198</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>46202</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>46202</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>46203</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45110</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45110</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45110</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44943</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45985</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>46211</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45113</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45701</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45989</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45209</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45314</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45036</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>44963</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45323</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45695</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45999</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>45999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45999</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45999</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45999</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>46001</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45469</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45740</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>46001</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45469</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45490</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>46001</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46230</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45233</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45708</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45572</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44865</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>46009</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46009</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>46009</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45632</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45728</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45224</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45525</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45754</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45474</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>46243</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>46243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45796</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>46042</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>46287</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>46288</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>46288</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>46288</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>46195</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>46244</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>46045</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>46287</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45526</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45408</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>46049</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46050</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>46199</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45805</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>46009</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>46058</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>46058</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46059</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>46128</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45811</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45818</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>46069</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45483</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>46069</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>46252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46296</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46295</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45832</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>45805</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45832</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45691</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45490</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45792</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45792</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46210</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45482</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44711</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45012</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45838</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45530</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46098</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46099</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44602</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45489</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45645</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45386</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>46105</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46105</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46106</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>46302</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>44981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44984</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>46114</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46121</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>46126</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46127</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44656</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>46128</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45756</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>46265</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>44908</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46307</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45834</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45280</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44994</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44914</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45763</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45985</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>46007</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45908</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>44914</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45979</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>46266</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46309</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>44995</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>46007</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46309</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>44539</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45490</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>46267</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45218</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45691</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>46266</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45931</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45908</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45908</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45490</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45931</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45379</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45968</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45572</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45432</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45884</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46314</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44951</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45832</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45348</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>46272</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45567</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45560</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45252</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44630</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>46141</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>46141</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>46141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45022</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44980</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45986</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45372</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>46146</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>45448</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>46147</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>46147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>45182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45580</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45695</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45695</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44713</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45553</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45603</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45601</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45604</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45691</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45603</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45090</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45244</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44987</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44970</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45103</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>45103</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45385</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>44613</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45329</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45034</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>44973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45408</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45625</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44978</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44663</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>44818</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45267</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45041</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45012</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45092</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45110</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>44733</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>45110</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45245</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45198</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45320</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45056</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44900</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45252</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>44836</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45435</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44915</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45098</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45092</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45369</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45369</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45208</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45280</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45280</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45391</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45240</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45240</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45147</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45519</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45096</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>44539</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44995</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>44995</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>44547</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45373</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44965</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45643</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45411</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>44621</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45043</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45022</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45601</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45580</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>44494</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44573</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45580</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45223</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45075</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45204</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44551</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45644</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45198</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45610</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45567</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45091</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>44547</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45208</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45385</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45691</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>44608</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45708</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45204</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45207</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45531</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45147</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45687</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45254</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44711</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>45098</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>44818</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45113</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>44749</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45110</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45169</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45408</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45204</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>44756</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45240</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45754</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45317</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45448</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45254</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45531</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45349</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>44503</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>44917</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45330</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>44945</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45448</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>45015</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45372</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>45294</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>45274</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45589</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>44879</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44621</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45215</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45523</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>45539</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>45448</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45258</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45433</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44865</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45720</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>44743</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>44585</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>44917</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>44951</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45526</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45369</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>44685</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44594</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>44665</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44634</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>45357</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45615</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45078</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45357</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>45287</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>45477</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45477</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45195</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>44988</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45476</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45357</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45470</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>44979</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45889</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45954</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>46009</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45468</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>46197</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
